--- a/data/google_maps.xlsx
+++ b/data/google_maps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,24 +476,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vivera Grande (Hotel)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>McKingstown at Dindigul</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="D2" t="n">
-        <v>435553</v>
+        <v>4694</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19, Palani Rd, New Agraharam, Begambur, Tamil Nadu 624001</t>
+          <t>Vani Vilas Nagar, 25A, Society Street, Thadicombu Rd, opp. Punjab National Bank, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04512423237</t>
+          <t>09840520026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -502,31 +506,35 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Vivera+Grande+%28Hotel%29/data=!4m10!3m9!1s0x3b00aa5ef9ab643d:0xd7a21d2a5ecd9f81!5m2!4m1!1i2!8m2!3d10.3666649!4d77.9772972!16s%2Fg%2F11bwtdlyt9!19sChIJPWSr-V6qADsRgZ_NXiodotc?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/McKingstown+at+Dindigul/data=!4m7!3m6!1s0x3b00abab75c0a37d:0x4994202a643ac269!8m2!3d10.3668328!4d77.9698631!16s%2Fg%2F11z0mppqnf!19sChIJfaPAdaurADsRacI6ZCoglEk?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vari Park</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Head Lines BARBER SHOP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hair salon</t>
+        </is>
+      </c>
       <c r="C3" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="D3" t="n">
-        <v>42725</v>
+        <v>4916</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>41, Dindigul - Palani Rd, New Agraharam, Begambur, Dindigul, Tamil Nadu 624001</t>
+          <t>RM Colony, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>09150007202</t>
+          <t>06374765528</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -535,31 +543,35 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Vari+Park/data=!4m10!3m9!1s0x3b00abc4111e3c63:0x55466207c1f2259c!5m2!4m1!1i2!8m2!3d10.3667453!4d77.9788191!16s%2Fg%2F11rs2tsbmk!19sChIJYzweEcSrADsRnCXywQdiRlU?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Head+Lines+BARBER+SHOP/data=!4m7!3m6!1s0x3b00aba1be8cd0ad:0xebf240bfd6680d15!8m2!3d10.3755076!4d77.9742679!16s%2Fg%2F11rf6pd_md!19sChIJrdCMvqGrADsRFQ1o1r9A8us?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hotel PVK Grand</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Scissor Signature</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>402513</v>
+        <v>505</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80, Thadicombu Rd, Ashok Nagar, Dindigul, Tamil Nadu 624001</t>
+          <t>7th Cross St, RM Colony, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>08098340099</t>
+          <t>06380748486</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -568,31 +580,35 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+PVK+Grand/data=!4m10!3m9!1s0x3b00aaf123f0fd6f:0xb27ed6d924c7520d!5m2!4m1!1i2!8m2!3d10.3739863!4d77.9679027!16s%2Fg%2F11b8yh5jc6!19sChIJb_3wI_GqADsRDVLHJNnWfrI?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Scissor+Signature/data=!4m7!3m6!1s0x3b00aba6d904eac9:0x77295fa594ba1ddf!8m2!3d10.3751061!4d77.9758683!16s%2Fg%2F11y_drcl7x!19sChIJyeoE2aarADsR3x26lKVfKXc?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parsons Court</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>AK BARBERSHOP AND TATTOO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hair salon</t>
+        </is>
+      </c>
       <c r="C5" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="D5" t="n">
-        <v>412390</v>
+        <v>4966</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>85, Mengles Rd, Mendonsa Colony, Nagal Nagar, Tamil Nadu 624003</t>
+          <t>Soundharaja complex, Soundararaja Airport Nagar, Dindigul, Tamil Nadu 624005</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09677702007</t>
+          <t>08012268804</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -601,64 +617,68 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Parsons+Court/data=!4m10!3m9!1s0x3b00aa508f3e82ef:0xc0857451925132a0!5m2!4m1!1i2!8m2!3d10.3584225!4d77.9819624!16s%2Fg%2F1th1sh0z!19sChIJ74I-j1CqADsRoDJRklF0hcA?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/AK+BARBERSHOP+AND+TATTOO/data=!4m7!3m6!1s0x3b00a9c13825cbd7:0x600e9af2151e781c!8m2!3d10.3605308!4d78.0204587!16s%2Fg%2F11p77bqh7c!19sChIJ18slOMGpADsRHHgeFfKaDmA?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hotel Chenduran Park</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>Sri Imaya Hair Designers</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>381204</v>
+        <v>45313</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33/1, Old RMS Rd, near Railway Station, Mendonsa Colony, Nagal Nagar, Tamil Nadu 624003</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>09787280005</t>
-        </is>
-      </c>
+          <t>AMC Rd, Mendonsa Colony, Dindigul, Tamil Nadu 624003</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+Chenduran+Park/data=!4m10!3m9!1s0x3b00aa5440000081:0xa97cc4bdfe5e8b68!5m2!4m1!1i2!8m2!3d10.353662!4d77.982219!16s%2Fg%2F12mm84mlg!19sChIJgQAAQFSqADsRaIte_r3EfKk?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Sri+Imaya+Hair+Designers/data=!4m7!3m6!1s0x3b00aa5aee4072f7:0x1db614504c76fdd7!8m2!3d10.3608769!4d77.9832478!16s%2Fg%2F11cmgtjbbs!19sChIJ93JA7lqqADsR1_12TFAUth0?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dolphin Hotels</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>Toni&amp;Guy Essensuals Dindigul RM Colony</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Health and beauty shop</t>
+        </is>
+      </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="D7" t="n">
-        <v>35388</v>
+        <v>48826</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14, Chatram St, New Agraharam, Begambur, Dindigul, Tamil Nadu 624001</t>
+          <t>Toni &amp; Guy Essensuals, opposite SAI VELAN RESIDENCY, RM Colony, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>08754031791</t>
+          <t>08304838383</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -667,31 +687,35 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Dolphin+Hotels/data=!4m10!3m9!1s0x3b00aaf406d86d73:0x7706d64999014409!5m2!4m1!1i2!8m2!3d10.3643572!4d77.9731073!16s%2Fg%2F1q5gnngqt!19sChIJc23YBvSqADsRCUQBmUnWBnc?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Toni%26Guy+Essensuals+Dindigul+RM+Colony/data=!4m7!3m6!1s0x3b00ab3986e1febd:0xbf27eb7c0e25595f!8m2!3d10.3731772!4d77.9718917!16s%2Fg%2F11hzl_w4km!19sChIJvf7hhjmrADsRX1klDnzrJ78?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hotel Parvathy's</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>Avm barbershop branch 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="D8" t="n">
-        <v>41420</v>
+        <v>4729</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14, Kovil Street, 45, Katcheri St, Dindigul, Tamil Nadu 624001</t>
+          <t>Malaipatty Rd, SIDCO Industrial Estate, Dindigul, Tamil Nadu 624003</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09677702009</t>
+          <t>09500400487</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -700,31 +724,35 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+Parvathy%27s/data=!4m10!3m9!1s0x3b00aaf67b8d37d9:0x27bfe680f4143b66!5m2!4m1!1i2!8m2!3d10.3636655!4d77.9714556!16s%2Fg%2F11f5lyb_gj!19sChIJ2TeNe_aqADsRZjsU9IDmvyc?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Avm+barbershop+branch+1/data=!4m7!3m6!1s0x3b00ab0d8e025e79:0x48198aed2a5ccf4b!8m2!3d10.3495214!4d77.9876314!16s%2Fg%2F11g0wp_s9_!19sChIJeV4Cjg2rADsRS89cKu2KGUg?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DAWOOD RESIDENCY</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>friends Trends family hair &amp; beauty saloon</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="D9" t="n">
-        <v>43829</v>
+        <v>48479</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1/28A MUTHU TOWER GANDHJI NEW ROAD, Anguvillas Irakkam Junction, 251/8, Gandhiji New Rd, near THIPPU SULTAN MANI MANDAPAM, Mettupatti, Dindigul, Tamil Nadu 624002</t>
+          <t>38, Palani Rd, opposite Sonna tower, New Agraharam, Begambur, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07868008080</t>
+          <t>09688896060</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -733,31 +761,35 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/DAWOOD+RESIDENCY/data=!4m10!3m9!1s0x3b00ab4298407ae7:0xf0d8446526fa4727!5m2!4m1!1i2!8m2!3d10.3561366!4d77.9702751!16s%2Fg%2F11fmxt3785!19sChIJ53pAmEKrADsRJ0f6JmVE2PA?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/friends+Trends+family+hair+%26+beauty+saloon/data=!4m7!3m6!1s0x3b00aa5e87383f67:0x634c93e93da6ace0!8m2!3d10.3669533!4d77.9792155!16s%2Fg%2F11gbp636bj!19sChIJZz84h16qADsR4KymPemTTGM?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Townhouse by OYO Dindigul Rock Fort Formerly Ramora Grand</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>Toni&amp;Guy Essensuals Dindigul (Main)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hair salon</t>
+        </is>
+      </c>
       <c r="C10" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="D10" t="n">
-        <v>39763</v>
+        <v>471185</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75, Thadicombu Rd, Meenachinayakkanpatti, Dindigul, Tamil Nadu 624001</t>
+          <t>I/6, toni&amp;guy essensuals, Sree Towers, No. 46, near Dindigul Railway Station, Indira Nagar, Nagal Nagar, Tamil Nadu 624003</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01244330599</t>
+          <t>07373102222</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -766,31 +798,35 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Townhouse+by+OYO+Dindigul+Rock+Fort+Formerly+Ramora+Grand/data=!4m10!3m9!1s0x3b00abe8f851bd5b:0x41633a1b2da4f737!5m2!4m1!1i2!8m2!3d10.3727456!4d77.9677958!16s%2Fg%2F11h12gl8rc!19sChIJW71R-OirADsRN_ekLRs6Y0E?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Toni%26Guy+Essensuals+Dindigul+%28Main%29/data=!4m7!3m6!1s0x3b00aa51eee91013:0x1212285d5a375ede!8m2!3d10.3544413!4d77.9843544!16s%2Fg%2F11b6pj8fbh!19sChIJExDp7lGqADsR3l43Wl0oEhI?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hotel Sethu Residenccy Dindigul</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Green Trends Unisex Hair &amp; Style Salon</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C11" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="D11" t="n">
-        <v>41480</v>
+        <v>482779</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9X9H+3GQ, 10, Krishna Rao 3rd St, behind Sona Tower, Pandian Nagar, Nehruji Nagar, Dindigul, Tamil Nadu 624001</t>
+          <t>7A,COOPERATIVE COLONY FIRST FLOOR, 7A, Trichy - Dindugal Rd, Cooperative Colony, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>09488175068</t>
+          <t>09600990022</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -799,60 +835,72 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+Sethu+Residenccy+Dindigul/data=!4m10!3m9!1s0x3b00aa701f8c5761:0x2ed82505a887d286!5m2!4m1!1i2!8m2!3d10.3678206!4d77.9783242!16s%2Fg%2F11ggb27n6g!19sChIJYVeMH3CqADsRhtKHqAUl2C4?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Green+Trends+Unisex+Hair+%26+Style+Salon/data=!4m7!3m6!1s0x3b00abebf11842d7:0x551b18c2842e82ef!8m2!3d10.3665749!4d77.9793161!16s%2Fg%2F11flc1dlss!19sChIJ10IY8eurADsR74IuhMIYG1U?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SVS Grand</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Avm barbershop branch 2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D12" t="n">
-        <v>40363</v>
+        <v>3825</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racecourse Road 1720/4C2, RACE COURSE ROAD, Round Rd, Dindigul, Tamil Nadu 624005</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>Unnamed Road, near Arivu Thirukovil, Chinniahpuram, Dindigul, Tamil Nadu 624004</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>09500400487</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/SVS+Grand/data=!4m10!3m9!1s0x3b00aa4f8629d5c9:0xf4c5f5720e9e1738!5m2!4m1!1i2!8m2!3d10.3591767!4d77.9866863!16s%2Fg%2F11rhc8b5d6!19sChIJydUphk-qADsROBeeDnL1xfQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Avm+barbershop+branch+2/data=!4m7!3m6!1s0x3b00ab6748969773:0x66a651cb6c640bc6!8m2!3d10.3805204!4d77.9764583!16s%2Fg%2F11hzflm4x8!19sChIJc5eWSGerADsRxgtkbMtRpmY?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L.R.R.TOWERS (LODGE)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>Be u for men Professional Salon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C13" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="D13" t="n">
-        <v>35402</v>
+        <v>47114</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36-F, bus stop, 1, Palani Rd, Ayyankulam, Dindigul, Tamil Nadu 624002</t>
+          <t>30B Ramnagar Roja 2nd Street, Round Rd, Tamil Nadu 624005</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>04512900339</t>
+          <t>09080160646</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -861,31 +909,35 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/L.R.R.TOWERS+%28LODGE%29/data=!4m10!3m9!1s0x3b00aaf27f17aea3:0xb6dc318638ba2a3a!5m2!4m1!1i2!8m2!3d10.3662432!4d77.9625939!16s%2Fg%2F11cm0kv0lq!19sChIJo64Xf_KqADsROiq6OIYx3LY?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Be+u+for+men+Professional+Salon/data=!4m7!3m6!1s0x3b00aba820d7dd71:0xfed7fe4e1f2edac2!8m2!3d10.363486!4d77.9883199!16s%2Fg%2F11jrr13sw7!19sChIJcd3XIKirADsRwtouH07-1_4?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JEYAM RESIDENCY</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>Anbu Hi-Cut Barber Shop</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="D14" t="n">
-        <v>451265</v>
+        <v>437</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>No 12 &amp; 13, Thadicombu Road,, near M.V.M. College, Dindigul, Tamil Nadu 624001</t>
+          <t>Complex, Ponnagaram, Dindigul, Suba Nagar, Tamil Nadu 624003</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>09787188555</t>
+          <t>09514916559</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -894,31 +946,35 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/JEYAM+RESIDENCY/data=!4m10!3m9!1s0x3b00aa8fed5d3957:0xd66765c5e738ee00!5m2!4m1!1i2!8m2!3d10.3784464!4d77.9662139!16s%2Fg%2F11dxl2_nc9!19sChIJVzld7Y-qADsRAO4458VlZ9Y?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Anbu+Hi-Cut+Barber+Shop/data=!4m7!3m6!1s0x3b00ab453af0fdc7:0x73c592d396e5edee!8m2!3d10.3370209!4d77.9965135!16s%2Fg%2F11f6cqg6hl!19sChIJx_3wOkWrADsR7u3lltOSxXM?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAVAN VELA GRAND</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>STUDIO11 FAMILY SALON MENGLES ROAD DINDIGUL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="D15" t="n">
-        <v>46199</v>
+        <v>491193</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bye Pass, Om Sakthi Nagar, Dindigul - Palani Rd, Kottapatti, Pallapatti, Tamil Nadu 624002</t>
+          <t>Sri Mahalakshmi tower 1st Floor 50 Mengles road, Court Rd, Parsons, Dindigul, Tamil Nadu 624003</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08940444648</t>
+          <t>06384002003</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -927,31 +983,35 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/PAVAN+VELA+GRAND/data=!4m10!3m9!1s0x3b00aabe2585688f:0x49a835575dc00638!5m2!4m1!1i2!8m2!3d10.3707531!4d77.9503824!16s%2Fg%2F11mcd6qyvx!19sChIJj2iFJb6qADsROAbAXVc1qEk?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/STUDIO11+FAMILY+SALON+MENGLES+ROAD+DINDIGUL/data=!4m7!3m6!1s0x3b00ab324174092b:0xf1783f97755a016b!8m2!3d10.3600787!4d77.9830077!16s%2Fg%2F11y1ds8krp!19sChIJKwl0QTKrADsRawFadZc_ePE?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Suthanthira Stay Inn</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>Studio11 Family Salon Collectorate Dgl</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D16" t="n">
-        <v>48501</v>
+        <v>49654</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trichy - Dindugal Rd, opp. DCC Bank Muthunagar, Cooperative Nagar, Dindigul, Tamil Nadu 624005</t>
+          <t>veluchamy complex, opp. collectorate, Chennamanayakkanpatti, Dindigul, Tamil Nadu 624004</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07273000044</t>
+          <t>06384002266</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -960,31 +1020,35 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Suthanthira+Stay+Inn/data=!4m10!3m9!1s0x3b00abd1d765e967:0xdff5fcd9f1bf4d70!5m2!4m1!1i2!8m2!3d10.374526!4d77.9907384!16s%2Fg%2F11ln_lk1vn!19sChIJZ-ll19GrADsRcE2_8dn89d8?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Studio11+Family+Salon+Collectorate+Dgl/data=!4m7!3m6!1s0x3baa01414256fd63:0xbfd59988a3b7dcbb!8m2!3d10.3924769!4d77.960775!16s%2Fg%2F11mw4wtwxb!19sChIJY_1WQkEBqjsRu9y3o4iZ1b8?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hotel AKMG - Classic</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>The Shine Family Salon &amp; Bridal Studio</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C17" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="D17" t="n">
-        <v>34197</v>
+        <v>4997</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15, Dindigul - Palani Rd, New Agraharam, Nehruji Nagar, Tamil Nadu 624001</t>
+          <t>1st floor, City tower, 33/1, Batlagundu Road, Mohamadiyapuram, Begambur, Dindigul, Tamil Nadu 624002</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09486409785</t>
+          <t>09500610062</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -993,64 +1057,68 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+AKMG+-+Classic/data=!4m10!3m9!1s0x3b00aa5efc343007:0xb9080a6f7ca4e940!5m2!4m1!1i2!8m2!3d10.3665767!4d77.9768726!16s%2Fg%2F11dxszgdsn!19sChIJBzA0_F6qADsRQOmkfG8KCLk?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/The+Shine+Family+Salon+%26+Bridal+Studio/data=!4m7!3m6!1s0x3b074fca7711d4ad:0x7b74d1b6796d4b98!8m2!3d10.3557363!4d77.9639306!16s%2Fg%2F11mkv_1_y9!19sChIJrdQRd8pPBzsRmEttebbRdHs?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hotel ZHANANA Inn</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>VINTAGE TOWN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C18" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>38236</v>
+        <v>501</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9X95+2X4, Murugabhavanam, 93, Palani Rd, Meenachinayakkanpatti, Dindigul, Tamil Nadu 624002</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>08903330346</t>
-        </is>
-      </c>
+          <t>Thadikombu Road, Society St, near Punjab National Bank, Dindigul, Tamil Nadu 624001</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+ZHANANA+Inn/data=!4m10!3m9!1s0x3b00abb72f354ce7:0x2d91984f878cbcb2!5m2!4m1!1i2!8m2!3d10.3674892!4d77.9599919!16s%2Fg%2F11g4lgb51s!19sChIJ50w1L7erADsRsryMh0-YkS0?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/VINTAGE+TOWN/data=!4m7!3m6!1s0x3b00ab06c21c9f35:0xab3078949953ef2b!8m2!3d10.3669122!4d77.9698692!16s%2Fg%2F11yv49zsh_!19sChIJNZ8cwgarADsRK-9TmZR4MKs?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>The Swagath Grande</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>Toni &amp; Guy Dindigul</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hairdresser</t>
+        </is>
+      </c>
       <c r="C19" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="D19" t="n">
-        <v>42215</v>
+        <v>48456</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>109 D, 109 D, NVGB Hall Rd, EB Colony, Nagal Nagar, Tamil Nadu 624003</t>
+          <t>Second Floor, No 42, Palani Rd, opposite Sona Tower, New Agraharam, Begambur, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09994553527</t>
+          <t>07092920001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1059,31 +1127,35 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/The+Swagath+Grande/data=!4m10!3m9!1s0x3b00ab20fecc7c31:0x1541bb6a3c8cc8c0!5m2!4m1!1i2!8m2!3d10.3557754!4d77.9789393!16s%2Fg%2F11vjykw0td!19sChIJMXzM_iCrADsRwMiMPGq7QRU?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Toni+%26+Guy+Dindigul/data=!4m7!3m6!1s0x3b00ab31266fcccd:0xaea1ce0788e137f!8m2!3d10.3668302!4d77.9785428!16s%2Fg%2F11lv7v7_v6!19sChIJzcxvJjGrADsRfxOOeOAc6go?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mangai Towers</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>STUDIO JEI SALON</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C20" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="D20" t="n">
-        <v>34366</v>
+        <v>43366</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bengali market, 19, Chatram St, near Taxi Stand, New Agraharam, Begambur, Dindigul, Tamil Nadu 624001</t>
+          <t>RM COLONY,80 FEET ROAD, Nehruji Nagar, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>09842117111</t>
+          <t>06384369369</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1092,31 +1164,35 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mangai+Towers/data=!4m10!3m9!1s0x3b00aaf600bb8dcd:0x75c2dea9548d98d4!5m2!4m1!1i2!8m2!3d10.3640793!4d77.973515!16s%2Fg%2F1pp2vlscx!19sChIJzY27APaqADsR1JiNVKnewnU?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/STUDIO+JEI+SALON/data=!4m7!3m6!1s0x3b00aa66dc0460af:0x5b399bddf5c1384e!8m2!3d10.3731202!4d77.9807938!16s%2Fg%2F11bxg8mb5n!19sChIJr2AE3GaqADsRTjjB9d2bOVs?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BAVA LODGE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>Parksan Salon, Dindigul</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C21" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="D21" t="n">
-        <v>35168</v>
+        <v>48846</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dindigul - Natham - Singampunari-Tiruppattur-Karaikudi Rd, Nagal Nagar, Tamil Nadu 624003</t>
+          <t>No.18 A First Floor Narayana Nagar, Pillaiyarpalayam, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>09364220872</t>
+          <t>09843167997</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1125,31 +1201,35 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/BAVA+LODGE/data=!4m10!3m9!1s0x3b00ab3f9a47ba91:0xa548c7bd16212ac0!5m2!4m1!1i2!8m2!3d10.3520083!4d77.9813352!16s%2Fg%2F11fl8xqysg!19sChIJkbpHmj-rADsRwCohFr3HSKU?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Parksan+Salon,+Dindigul/data=!4m7!3m6!1s0x3b00ab83354fadbb:0xa0061cf935f774e5!8m2!3d10.3689157!4d77.9778748!16s%2Fg%2F11j1pfcxqf!19sChIJu61PNYOrADsR5XT3NfkcBqA?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JMA Garden Resorts</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>Style Zone</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hairdresser</t>
+        </is>
+      </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="D22" t="n">
-        <v>502</v>
+        <v>4964</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9X69+VQP, Village, Begambur, Thindukkal, Tamil Nadu 624001</t>
+          <t>SS complex, 1st floor,Siluvathur road, bypass road, near New siluvathu, near Karthik nursing Home, Tamil Nadu 624005</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>08940743256</t>
+          <t>09360721399</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1158,31 +1238,35 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/JMA+Garden+Resorts/data=!4m10!3m9!1s0x3b00aaf6c224eedd:0xdc5e699100188146!5m2!4m1!1i2!8m2!3d10.362219!4d77.969463!16s%2Fg%2F11lzj_c_yx!19sChIJ3e4kwvaqADsRRoEYAJFpXtw?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Style+Zone/data=!4m7!3m6!1s0x3b00ab5cb5ef51e9:0x49e8a4235c4047b4!8m2!3d10.3635558!4d77.9915762!16s%2Fg%2F11vjzrz_vj!19sChIJ6VHvtVyrADsRtEdAXCOk6Ek?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pandian Lodge</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>Naturals Salon</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C23" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="D23" t="n">
-        <v>3541</v>
+        <v>494949</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11, Abirami Amman Kovil St, Begambur, Dindigul, Tamil Nadu 624001</t>
+          <t>No 18, 2nd Floor, TNPK Forum, Dindigul - Palani Rd, above Reliance Super Store, Ashok Nagar, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>04512433013</t>
+          <t>09600680123</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1191,60 +1275,72 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Pandian+Lodge/data=!4m10!3m9!1s0x3b00aaf6635c7a8f:0x3e85596b266d1787!5m2!4m1!1i2!8m2!3d10.3634147!4d77.971458!16s%2Fg%2F11rkbtfp_z!19sChIJj3pcY_aqADsRhxdtJmtZhT4?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Naturals+Salon/data=!4m7!3m6!1s0x3b00ab1872189329:0x4404fd8e818aeef2!8m2!3d10.3655827!4d77.9706651!16s%2Fg%2F11jd1s42rk!19sChIJKZMYchirADsR8u6KgY79BEQ?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nivis Hotel and Bar</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>AK BABERSHOP BRANCH 2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C24" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>34254</v>
+        <v>501</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9XMG+G9R, Chinniahpuram, Dindigul, Tamil Nadu 624004</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>SHOP NUMBER 10, GTN SALAI, MSP SCHOOL ROAD, Masilamanipuram, Dindigul, Tamil Nadu 624005</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>06380021467</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Nivis+Hotel+and+Bar/data=!4m10!3m9!1s0x3b00aa7da43eeec5:0x66c3fdd06cd6f0a8!5m2!4m1!1i2!8m2!3d10.3838626!4d77.9758845!16s%2Fg%2F11cs34w5lq!19sChIJxe4-pH2qADsRqPDWbND9w2Y?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/AK+BABERSHOP+BRANCH+2/data=!4m7!3m6!1s0x3b00abf08abd59b7:0x5c57440b8c78785f!8m2!3d10.3654362!4d77.9887358!16s%2Fg%2F11x8lt9wpc!19sChIJt1m9ivCrADsRX3h4jAtEV1w?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SaiVelan Residency</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>Jai Hair Studio</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C25" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="D25" t="n">
-        <v>37355</v>
+        <v>4830</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>61/1-4, E.V.R Salai, 80Feet Road, West, Ashok Nagar, Dindigul, Tamil Nadu 624001</t>
+          <t>old, Karur Rd, N.S.Nagar, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>09344583918</t>
+          <t>07358455581</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1253,31 +1349,35 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/SaiVelan+Residency/data=!4m10!3m9!1s0x3b00ab50352bfe67:0x4bb2f9d990b1e321!5m2!4m1!1i2!8m2!3d10.3733347!4d77.9716625!16s%2Fg%2F11gn1w6b7k!19sChIJZ_4rNVCrADsRIeOxkNn5sks?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Jai+Hair+Studio/data=!4m7!3m6!1s0x3b00abf1e911c61f:0x3f053e4634c2dc45!8m2!3d10.390099!4d77.9951008!16s%2Fg%2F11tx6jx2zs!19sChIJH8YR6fGrADsRRdzCNEY-BT8?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hotel Vales Park</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>GREEN LOOK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C26" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="D26" t="n">
-        <v>391175</v>
+        <v>4876</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>49-A, Mengles Rd, EB Colony, Nagal Nagar, Tamil Nadu 624003</t>
+          <t>2/A, Palani Rd, New Agraharam, Govindapuram, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>08489211011</t>
+          <t>09113079511</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1286,97 +1386,101 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+Vales+Park/data=!4m10!3m9!1s0x3b00aa50ea0b247d:0x40da5527ceddfc34!5m2!4m1!1i2!8m2!3d10.3571738!4d77.980949!16s%2Fg%2F1wrghlv2!19sChIJfSQL6lCqADsRNPzdzidV2kA?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/GREEN+LOOK/data=!4m7!3m6!1s0x3b00ab32f4b03709:0x3d78fe457fc4c43b!8m2!3d10.3656933!4d77.9739993!16s%2Fg%2F11j841z4mf!19sChIJCTew9DKrADsRO8TEf0X-eD0?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mymoon Furnished Apartments</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>Janani beauty saloon</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C27" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="D27" t="n">
-        <v>4535</v>
+        <v>4913</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6,7,8, yasmin tower landmark SBI, 5, railady street, Mendonsa Colony, Tamil Nadu 624003</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>07550036500</t>
-        </is>
-      </c>
+          <t>Begambur, Tamil Nadu 624002</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mymoon+Furnished+Apartments/data=!4m10!3m9!1s0x3b00ab000f85edc9:0x17cd92cd2da8b355!5m2!4m1!1i2!8m2!3d10.352212!4d77.9820107!16s%2Fg%2F11wq0f8d_f!19sChIJye2FDwCrADsRVbOoLc2SzRc?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Janani+beauty+saloon/data=!4m7!3m6!1s0x3b00ab0012ef6d7f:0xba697fb87b12c589!8m2!3d10.3518364!4d77.9645828!16s%2Fg%2F11zb4d4db3!19sChIJf23vEgCrADsRicUSe7h_abo?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sree baalaaji bhavan</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>Royal Touch Mens</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="D28" t="n">
-        <v>401530</v>
+        <v>4316</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>40, Thiruvalluvar Salai, Spencer Compound, Dindigul, Tamil Nadu 624003</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>08220724444</t>
-        </is>
-      </c>
+          <t>133, Mengles Rd, Y.M.R, Mendonsa Colony, Dindigul, Tamil Nadu 624001</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sree+baalaaji+bhavan/data=!4m10!3m9!1s0x3b00aa599a8fdea3:0x52f5b0a746c11381!5m2!4m1!1i2!8m2!3d10.3604631!4d77.9787292!16s%2Fg%2F12hml5d6b!19sChIJo96PmlmqADsRgRPBRqew9VI?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Royal+Touch+Mens/data=!4m7!3m6!1s0x3b00aa5b112e7213:0x6a0c12221f3868f9!8m2!3d10.3626325!4d77.9834786!16s%2Fg%2F12q4tcbx5!19sChIJE3IuEVuqADsR-Wg4HyISDGo?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kumaran Residency</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>VIBE &amp; RADIANCE UNISEX SALON</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C29" t="n">
         <v>4.9</v>
       </c>
       <c r="D29" t="n">
-        <v>49875</v>
+        <v>49108</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palam Rajakkapatty,Door no 451, Survey no: 29/2A1 Anaipatty panchayat, Tamil Nadu 624002</t>
+          <t>1ST FLOOR, CITY TOWER, 33/1, BATLAGUNDU ROAD, Mohamadiyapuram, Begambur, Dindigul, Tamil Nadu 624002</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>09363034141</t>
+          <t>09500610062</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1385,31 +1489,35 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Kumaran+Residency/data=!4m10!3m9!1s0x3baa010064f4932f:0x99dcd2bacb8bec36!5m2!4m1!1i2!8m2!3d10.3922897!4d77.9313453!16s%2Fg%2F11w9ytkd0k!19sChIJL5P0ZAABqjsRNuyLy7rS3Jk?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/VIBE+%26+RADIANCE+UNISEX+SALON/data=!4m7!3m6!1s0x3b00ab001d42fe7f:0xd10becfea5009830!8m2!3d10.3557058!4d77.9639255!16s%2Fg%2F11wb_0vsqg!19sChIJf_5CHQCrADsRMJgApf7sC9E?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JPD Residency</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>MEERA BEAUTY CARE AND TRAINING INSTITUTE(PRO HD MAKEUP ARTIST / PRO HAIRSTYLIST/HAIR AND SKIN CARE WITH ADVANCED TECHNOLOGY)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C30" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>4127</v>
+        <v>50812</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82H3+9C3, SH 35, Ponnagaram, Tottanuthu, Tamil Nadu 624003</t>
+          <t>No.4 &amp; 5, Saravana Shopping Complex, Door No.3 Old, No.11, Chatram St, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>08870066928</t>
+          <t>07904368221</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1418,93 +1526,105 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/JPD+Residency/data=!4m10!3m9!1s0x3b00ab0045af6057:0x80aedf05bc506e13!5m2!4m1!1i2!8m2!3d10.3289251!4d78.0031459!16s%2Fg%2F11m6n66v0h!19sChIJV2CvRQCrADsRE25QvAXfroA?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/MEERA+BEAUTY+CARE+AND+TRAINING+INSTITUTE%28PRO+HD+MAKEUP+ARTIST+%2F+PRO+HAIRSTYLIST%2FHAIR+AND+SKIN+CARE+WITH+ADVANCED+TECHNOLOGY%29/data=!4m7!3m6!1s0x3b00ab7cf4d9d567:0xf7a7109ff6b37c3e!8m2!3d10.3644122!4d77.9723243!16s%2Fg%2F11h73xf39x!19sChIJZ9XZ9HyrADsRPnyz9p8Qp_c?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hotel Sky Park</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>STUDIEO Z FAMILY SALON AND BRIDAL STUDIO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C31" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>35341</v>
+        <v>50325</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16, Chatram St, New Agraharam, Begambur, Dindigul, Tamil Nadu 624001</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>RVR Complex, AMC Rd, near Chennai Silks, above Ashwin Sweets, Mendonsa Colony, Dindigul, Tamil Nadu 624003</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>08220246495</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+Sky+Park/data=!4m10!3m9!1s0x3b00aaf5e3889843:0x3fabe01241d7cca0!5m2!4m1!1i2!8m2!3d10.3642839!4d77.9732821!16s%2Fg%2F11g6vjlwmv!19sChIJQ5iI4_WqADsRoMzXQRLgqz8?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/STUDIEO+Z+FAMILY+SALON+AND+BRIDAL+STUDIO/data=!4m7!3m6!1s0x3b00ab25513b4d87:0x76787241a5d4ce52!8m2!3d10.3605814!4d77.983612!16s%2Fg%2F11vk7hw27v!19sChIJh007USWrADsRUs7UpUFyeHY?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hotel Maha Jyothi</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>Style zone</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hair salon</t>
+        </is>
+      </c>
       <c r="C32" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="D32" t="n">
-        <v>39407</v>
+        <v>4723</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8, Salai Rd, Spencer Compound, Dindigul, Tamil Nadu 624001</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>04512434313</t>
-        </is>
-      </c>
+          <t>Mohamadiyapuram, Begambur, Dindigul, Tamil Nadu 624002</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+Maha+Jyothi/data=!4m10!3m9!1s0x3b00aa59d3a1060d:0xa724d5ad567d92d4!5m2!4m1!1i2!8m2!3d10.3591997!4d77.9768253!16s%2Fg%2F12mm8bz65!19sChIJDQah01mqADsR1JJ9Vq3VJKc?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Style+zone/data=!4m7!3m6!1s0x3b00ab2caf7256f1:0xfae5739e65e38084!8m2!3d10.357826!4d77.9672146!16s%2Fg%2F11h2b4t2f4!19sChIJ8VZyryyrADsRhIDjZZ5z5fo?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Anand International</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>Naturals Salon</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C33" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="D33" t="n">
-        <v>3732</v>
+        <v>483038</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spencer Compound, Tamil Nadu 624003</t>
+          <t>9A, Round Rd, near Smb School, Ram Nagar, Elil Nagar, Dindigul, Tamil Nadu 624005</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>04512427510</t>
+          <t>08903341111</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -1513,31 +1633,35 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Anand+International/data=!4m10!3m9!1s0x3b00aa59c58347c1:0xe8d7aa25284cda9!5m2!4m1!1i2!8m2!3d10.3595675!4d77.9776521!16s%2Fg%2F1tctk6d4!19sChIJwUeDxVmqADsRqc2EUqJ6jQ4?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Naturals+Salon/data=!4m7!3m6!1s0x3b00aa5e7e4573c9:0xa7d1d6c8adf7c1c8!8m2!3d10.3633246!4d77.9896386!16s%2Fg%2F1264mrj_w!19sChIJyXNFfl6qADsRyMH3rcjW0ac?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hotel Iswarya</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>Studieo7 Family Salon and Bridal Studio</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="D34" t="n">
-        <v>30184</v>
+        <v>462147</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Spencer Compound, Dindigul, Tamil Nadu 624003</t>
+          <t>34A, Palani Rd, above suzuki showroom, New Agraharam, Nehruji Nagar, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>04512432324</t>
+          <t>08344456789</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1546,31 +1670,35 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+Iswarya/data=!4m10!3m9!1s0x3b00aa599911a953:0x49f500e827fb9370!5m2!4m1!1i2!8m2!3d10.361121!4d77.9783918!16s%2Fg%2F1yj2mkkv2!19sChIJU6kRmVmqADsRcJP7J-gA9Uk?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Studieo7+Family+Salon+and+Bridal+Studio/data=!4m7!3m6!1s0x3b00aa5e7f6b538f:0xddd0e21b57bb789d!8m2!3d10.3674013!4d77.9797139!16s%2Fg%2F11cmr1_hy4!19sChIJj1Nrf16qADsRnXi7Vxvi0N0?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rockfort Palace</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>Studieo7 Family salon &amp; Bridal Studio</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C35" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>38302</v>
+        <v>50805</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9X38+X8G, Kanyakumari Road, Begambur, Tamil Nadu 624002</t>
+          <t>Trichy - Dindugal Rd, near City Hospital, Cooperative Nagar, Dindigul, Tamil Nadu 624005</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>04512400855</t>
+          <t>08610406570</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1579,31 +1707,35 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Rockfort+Palace/data=!4m10!3m9!1s0x3b00aafbb008070f:0x291f7f37133e83d6!5m2!4m1!1i2!8m2!3d10.3549392!4d77.9658148!16s%2Fg%2F1hdzz8s28!19sChIJDwcIsPuqADsR1oM-Ezd_Hyk?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Studieo7+Family+salon+%26+Bridal+Studio/data=!4m7!3m6!1s0x3b00ab213387fe09:0xacb1157c3f4033d1!8m2!3d10.3731173!4d77.9896297!16s%2Fg%2F11lcr047qb!19sChIJCf6HMyGrADsR0TNAP3wVsaw?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Annai Residency</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>Sri Maha Beauty Salon and Academy</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Beautician</t>
+        </is>
+      </c>
       <c r="C36" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="D36" t="n">
-        <v>3225</v>
+        <v>49192</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>No: 18, Aarthi Theatre Rd, near St Joseph Hospital, Y.M.R. Patty, Karunanidhi Nagar, Anna Nagar, Tamil Nadu 624001</t>
+          <t>3, Ramanujam Nagar, Round Rd, Elil Nagar, Dindigul, Tamil Nadu 624005</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>09790518392</t>
+          <t>09789697397</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -1612,31 +1744,35 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Annai+Residency/data=!4m10!3m9!1s0x3b00aa5c8a81ba3f:0xe012482cc042c98f!5m2!4m1!1i2!8m2!3d10.3671123!4d77.9820086!16s%2Fg%2F11byt_6g05!19sChIJP7qBilyqADsRj8lCwCxIEuA?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Sri+Maha+Beauty+Salon+and+Academy/data=!4m7!3m6!1s0x3b00ab18615581ad:0xebce80ac9fb02678!8m2!3d10.3590552!4d77.9890546!16s%2Fg%2F11jbggjx8b!19sChIJrYFVYRirADsReCawn6yAzus?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OYO Flagship Habiba Noor Inn</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>STUDIO ONE UNISEX SALON (Bridal Makeup/Hair Spa/Advanced Facial and Haircut in Dindigul)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="D37" t="n">
-        <v>30162</v>
+        <v>4976</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34, Madurai Rd, Begambur, Tamil Nadu 624002</t>
+          <t>Bus Stand, 15, Spencers Compound, near Kurunji Lodge, opp. Dindigul, Tamil Nadu 624003</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>01246201165</t>
+          <t>08220246495</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1645,31 +1781,35 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/OYO+Flagship+Habiba+Noor+Inn/data=!4m10!3m9!1s0x3b00ab2f5daee1ed:0x5a7f22e7716020eb!5m2!4m1!1i2!8m2!3d10.3547955!4d77.9660617!16s%2Fg%2F11h3bgprtq!19sChIJ7eGuXS-rADsR6yBgcecif1o?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/STUDIO+ONE+UNISEX+SALON+%28Bridal+Makeup%2FHair+Spa%2FAdvanced+Facial+and+Haircut+in+Dindigul%29/data=!4m7!3m6!1s0x3b00ab4b86ff350f:0x73960ff2be323ede!8m2!3d10.3595215!4d77.9788327!16s%2Fg%2F11pv2690n6!19sChIJDzX_hkurADsR3j4yvvIPlnM?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Priyam Lodge</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>SRI SAI PRAKI BEAUTY PARLOUR &amp; TATTOO STUDIO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C38" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>36416</v>
+        <v>5046</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>76, N Car St, Dindigul, Tamil Nadu 624001</t>
+          <t>S Car St, near Venu Briyani, Ashok Nagar, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>07539958660</t>
+          <t>09894161244</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1678,31 +1818,35 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Priyam+Lodge/data=!4m10!3m9!1s0x3b00aaf6f608c977:0xf551f390a6724fe!5m2!4m1!1i2!8m2!3d10.3648597!4d77.9832879!16s%2Fg%2F11c5sk7vlg!19sChIJd8kI9vaqADsR_iRnCjkfVQ8?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/SRI+SAI+PRAKI+BEAUTY+PARLOUR+%26+TATTOO+STUDIO/data=!4m7!3m6!1s0x3b00abdb400d9aa3:0x5f3f0f580b206734!8m2!3d10.3668779!4d77.970222!16s%2Fg%2F11vrkhw3bq!19sChIJo5oNQNurADsRNGcgC1gPP18?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SRI VENKATESHWAR LODGE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>Varahi Trendz</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C39" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>38258</v>
+        <v>501</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>86, HEAD POST OFFICE ROAD, near Bus Stand, Mendonsa Colony, Dindigul, Tamil Nadu 624001</t>
+          <t>35,A, Varahi Trendz, Round Rd, opposite Naidu Mahal, Elil Nagar, Tamil Nadu 624005</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06369491393</t>
+          <t>09003444145</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -1711,26 +1855,30 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/SRI+VENKATESHWAR+LODGE/data=!4m10!3m9!1s0x3b00aa5a4c7cdabd:0x83c94ba9ed8798e1!5m2!4m1!1i2!8m2!3d10.3615002!4d77.9814251!16s%2Fg%2F11g6rpl7_7!19sChIJvdp8TFqqADsR4ZiH7alLyYM?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Varahi+Trendz/data=!4m7!3m6!1s0x3b00ab62b3ebd7c7:0xf8e6d1c3aedf0db2!8m2!3d10.3602873!4d77.9868696!16s%2Fg%2F11z9wn56l5!19sChIJx9frs2KrADsRsg3frsPR5vg?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hotel City Square</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>Best saloon</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C40" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>46171</v>
+        <v>501</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SF. No. 280/2A, Pillayarnatham Privu, Athur, Tamil Nadu 624002</t>
+          <t>8XXX+Q87, Rd, Sastri Nagar, Pallapatti, Dindigul, Tamil Nadu 624005</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1740,26 +1888,30 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hotel+City+Square/data=!4m10!3m9!1s0x3b00ab324d0fb8a3:0x81d7801ec30fa3a6!5m2!4m1!1i2!8m2!3d10.332379!4d77.931869!16s%2Fg%2F11yc647817!19sChIJo7gPTTKrADsRpqMPwx6A14E?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Best+saloon/data=!4m7!3m6!1s0x3b00ab00638ef5e3:0x2b4bd24125e8bb19!8m2!3d10.3494277!4d77.9982466!16s%2Fg%2F11mrqrrpfw!19sChIJ4_WOYwCrADsRGbvoJUHSSys?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Prakash Lodge</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>Shauthiyar Saloon for men</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C41" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>2645</v>
+        <v>501</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9X6H+389, Spencer Compound, Dindigul, Tamil Nadu 624003</t>
+          <t>9X3R+WC6, Mariyanatha Puram, Dindigul, Tamil Nadu 624003</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1769,31 +1921,35 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Prakash+Lodge/data=!4m10!3m9!1s0x3b00ab1a04782445:0x79a7a2c4deeba9fe!5m2!4m1!1i2!8m2!3d10.3601603!4d77.9783613!16s%2Fg%2F11g10mszz9!19sChIJRSR4BBqrADsR_qnr3sSip3k?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Shauthiyar+Saloon+for+men/data=!4m7!3m6!1s0x3b00ab007046d15d:0x732353f7c5b27464!8m2!3d10.3547812!4d77.991021!16s%2Fg%2F11vwn892kr!19sChIJXdFGcACrADsRZHSyxfdTI3M?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OYO 41328 Baboomas Rainbow Resort</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>Bright&amp;White</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Hair salon</t>
+        </is>
+      </c>
       <c r="C42" t="n">
         <v>3.9</v>
       </c>
       <c r="D42" t="n">
-        <v>39121</v>
+        <v>39164</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mullipadi Village Padiyur, Via, Dindigul, Tamil Nadu 624005</t>
+          <t>9XH9+964, 1st Cross St, RM Colony, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01246201165</t>
+          <t>04512460878</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -1802,31 +1958,35 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/OYO+41328+Baboomas+Rainbow+Resort/data=!4m10!3m9!1s0x3baa070dca039559:0x990195655cc906ec!5m2!4m1!1i2!8m2!3d10.4012487!4d78.0224563!16s%2Fg%2F11h0vbn6dp!19sChIJWZUDyg0HqjsR7AbJXGWVAZk?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Bright%26White/data=!4m7!3m6!1s0x3b00aa8f2d74374b:0xd8e36a02e06c29b6!8m2!3d10.3783847!4d77.968064!16s%2Fg%2F11c31n0l5c!19sChIJSzd0LY-qADsRtils4AJq49g?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Anbalaya Oldage Home</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>Miruthu Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
       <c r="C43" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D43" t="n">
-        <v>469</v>
+        <v>48143</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anbalaya Campus, Thirupathi Nagar, Sellamanthadi, Tamil Nadu 624005</t>
+          <t>Vinayaga 'B' section, Plot no: 26A, Karur Rd, 2nd Cross St, N.S.Nagar, Dindigul, Tamil Nadu 624001</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>09842177203</t>
+          <t>08428850808</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -1835,40 +1995,579 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Anbalaya+Oldage+Home/data=!4m10!3m9!1s0x3baa00b8ec4c4e19:0x88886636e32e040e!5m2!4m1!1i2!8m2!3d10.4027048!4d78.0008839!16s%2Fg%2F11hczbs3h6!19sChIJGU5M7LgAqjsRDgQu4zZmiIg?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Miruthu+Beauty+Parlour/data=!4m7!3m6!1s0x3b00aa749f9ce0c9:0x505f6c169d4cb7c7!8m2!3d10.3871326!4d77.995353!16s%2Fg%2F11dymnmnqs!19sChIJyeCcn3SqADsRx7dMnRZsX1A?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Praniv Plaza</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>NOWMI MEN SALON</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
       <c r="C44" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>35177</v>
+        <v>304</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Palani Rd, New Agraharam, Begambur, Tamil Nadu 624001</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>08344411011</t>
-        </is>
-      </c>
+          <t>72/1, Mettupatti Rdopp. Treasury Office, Anwariyya MahallaNagal Nagar, Dindigul, Tamil Nadu 624002</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Praniv+Plaza/data=!4m10!3m9!1s0x3b00aa5e88e25449:0xa6fd9e98810b8eb3!5m2!4m1!1i2!8m2!3d10.3666868!4d77.9789185!16s%2Fg%2F1pt_2lpfp!19sChIJSVTiiF6qADsRs44LgZie_aY?authuser=0&amp;hl=en&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/NOWMI+MEN+SALON/data=!4m7!3m6!1s0x3b00ab002326795d:0xc7a16c2f466aee63!8m2!3d10.347745!4d77.9946882!16s%2Fg%2F11yp6f3s96!19sChIJXXkmIwCrADsRY-5qRi9socc?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>I Can Beauty Tent</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4891</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Devi Priya Complex, Chennamanayakkan Patti Road, near Shifa Hospital, Collectorate, Tamil Nadu 624004</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>08072808971</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/I+Can+Beauty+Tent/data=!4m7!3m6!1s0x3b00ab57261a5a51:0x2c72bd7153d1f60a!8m2!3d10.3900188!4d77.9615078!16s%2Fg%2F11w8l196d_!19sChIJUVoaJlerADsRCvbRU3G9ciw?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AK BARBERSHOP and tattoo branch 2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GTN SALAI, Round Rd, Dindigul, Tamil Nadu 624005</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>06380021467</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/AK+BARBERSHOP+and+tattoo+branch+2/data=!4m7!3m6!1s0x3b00ab8ed3610ee7:0x4e573814c079ac9f!8m2!3d10.364801!4d77.9887388!16s%2Fg%2F11x8lt882x!19sChIJ5w5h046rADsRn6x5wBQ4V04?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LN Artistry Unisex Salon and Makeup Studio</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>48110</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>5/949,Co-operative Nagar, Malligai street,Trichy Road,Dindigul- 624 001, Dindigul, Tamil Nadu 624005</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>07373992345</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/LN+Artistry+Unisex+Salon+and+Makeup+Studio/data=!4m7!3m6!1s0x3b00abd8b4f7e307:0xb891c0a6e4765dfc!8m2!3d10.3744762!4d77.9902573!16s%2Fg%2F11sqdb9k_j!19sChIJB-P3tNirADsR_F125KbAkbg?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hair Saloon</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hair salon</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>9XFH+FR4, 9th Cross St, Nehruji Nagar, Dindigul, Tamil Nadu 624001</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hair+Saloon/data=!4m7!3m6!1s0x3b00aa61334b42fb:0xd3a1d34ef9981061!8m2!3d10.373646!4d77.9795881!16s%2Fg%2F11bwq934nj!19sChIJ-0JLM2GqADsRYRCY-U7TodM?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Beauty Trends Parlour</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4961</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>S.S. Complex, Siluvathur Rd, near Karthik Nursing Home, Masilamanipuram, Dindigul, Tamil Nadu 624005</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>09790576478</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Beauty+Trends+Parlour/data=!4m7!3m6!1s0x3b00aa46a29f34fd:0xc27e9e0a14c9ff09!8m2!3d10.3635502!4d77.9916395!16s%2Fg%2F11hd1lrmxj!19sChIJ_TSfokaqADsRCf_JFAqefsI?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Vantha Vettuvom Dindigul</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4032</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>VANTHAVETTUVOM, 62/1, Palani Rd, near Sakthi Talkies, opposite HP Petrol bunk, Begambur, Tamil Nadu 624001</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>08122105002</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Vantha+Vettuvom+Dindigul/data=!4m7!3m6!1s0x3b00ab84cea17d89:0xd5dda6f6bea00060!8m2!3d10.3657905!4d77.967897!16s%2Fg%2F11y64_gk12!19sChIJiX2hzoSrADsRYACgvvam3dU?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Divyaa'S Acu &amp; Beauty care Training Institute</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4992</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>B5, Society Building, opposite St. Joseph Hospital, Dindigul, Tamil Nadu 624001</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>09123542457</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Divyaa%27S+Acu+%26+Beauty+care+Training+Institute/data=!4m7!3m6!1s0x3b00ab1ac0c77ef9:0xd5dda982a796164f!8m2!3d10.36855!4d77.9820434!16s%2Fg%2F11y34v1f7b!19sChIJ-X7HwBqrADsRTxaWp4Kp3dU?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Justforyoubeautyparlour&amp; academy</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5011</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Indian petrol pump, Ourlady school, nearby Madurai Road, opp. Behambur post dindigul, Dindigul, Tamil Nadu 624002</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>09566457664</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Justforyoubeautyparlour%26+academy/data=!4m7!3m6!1s0x3b00aba4fd6a9a91:0x5a8707dba4f0d9d3!8m2!3d10.3518582!4d77.9644933!16s%2Fg%2F11s9dk48dw!19sChIJkZpq_aSrADsR09nwpNsHh1o?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Prince beauty centre &amp; cosmetic</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cosmetics store</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4550</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>13.first floor, PC&amp;CO Complex, N Car St, Begambur, Dindigul, Tamil Nadu 624001</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>09600287090</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Prince+beauty+centre+%26+cosmetic/data=!4m7!3m6!1s0x3b00ab4e3a4b5aff:0x231e4968cd32364e!8m2!3d10.3645969!4d77.9700675!16s%2Fg%2F11s16pqlm_!19sChIJ_1pLOk6rADsRTjYyzWhJHiM?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Eyesome Unisex Salon</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>508</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>No.8, Apollo medical upstairs, 1, Thiruvalluvar Salai, Spencer Compound, Dindigul, Tamil Nadu 624003</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Eyesome+Unisex+Salon/data=!4m7!3m6!1s0x3b00abe81fc86af7:0x6d1fd35427fe6b35!8m2!3d10.3593674!4d77.9782852!16s%2Fg%2F11l3n_xk0z!19sChIJ92rIH-irADsRNWv-J1TTH20?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Merina's Beauty Salon</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Beauty Parlour</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5037</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SMBM school back side, GTN Sali Rd, Masilamanipuram, Dindigul, Tamil Nadu 624005</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>09597724463</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Merina%27s+Beauty+Salon/data=!4m7!3m6!1s0x3b00ab0023df5915:0x2a830e7f53c08567!8m2!3d10.3637295!4d77.9904014!16s%2Fg%2F11wwt3z7k2!19sChIJFVnfIwCrADsRZ4XAU38Ogyo?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Barbers Hut</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hair salon</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>325</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>9XGW+J2H, Trichy - Dindugal Rd, Lakshmi Nagar, NGO Colony, Cooperative Nagar, Dindigul, Tamil Nadu 624005</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Barbers+Hut/data=!4m7!3m6!1s0x3b00aba2bb70c93f:0x5b2ef050016e5de!8m2!3d10.3763905!4d77.9951037!16s%2Fg%2F11vd_1dxz1!19sChIJP8lwu6KrADsR3uUWAAXvsgU?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>KARTHIK HAIR FAIR</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Barber shop</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>501</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>9XHX JXV, Dindigul, Tamil Nadu 624005</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>09715543899</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/KARTHIK+HAIR+FAIR/data=!4m7!3m6!1s0x3b00abbae712b7ff:0x90d31dca566a774e!8m2!3d10.3788355!4d77.9996574!16s%2Fg%2F11vk3y6r__!19sChIJ_7cS57qrADsRTndqVsod05A?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Stylish Beauty Parlour &amp; Bridal Makeup Studio</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4855</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>No. 29, 3, Siluvathur Rd, Y.M.R. Patty, Elil Nagar, Dindigul, Tamil Nadu 624001</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>08695498147</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Stylish+Beauty+Parlour+%26+Bridal+Makeup+Studio/data=!4m7!3m6!1s0x3b00ab0948cbcbc7:0x63f4f68b974e5b92!8m2!3d10.3636958!4d77.98382!16s%2Fg%2F11fmrj6ch0!19sChIJx8vLSAmrADsRkltOl4v29GM?authuser=0&amp;hl=en&amp;rclk=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Vibez Salon For Men</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hair salon</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>504</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Taj Complex, Bus Stand, Road, AMC Rd, Elil Nagar, Dindigul, Tamil Nadu 624005</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>08124885880</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Vibez+Salon+For+Men/data=!4m7!3m6!1s0x3b00ab41e18254ad:0xf882f470e3152ad9!8m2!3d10.3615392!4d77.991887!16s%2Fg%2F11yj5_1hj8!19sChIJrVSC4UGrADsR2SoV43D0gvg?authuser=0&amp;hl=en&amp;rclk=1</t>
         </is>
       </c>
     </row>
